--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.74306169010591</v>
+        <v>6.295747524642211</v>
       </c>
       <c r="D2" t="n">
-        <v>41.2034139799019</v>
+        <v>6.695554771734059</v>
       </c>
       <c r="E2" t="n">
-        <v>19.37026358447066</v>
+        <v>3.147667832476482</v>
       </c>
       <c r="F2" t="n">
-        <v>17.62451984973924</v>
+        <v>2.863984475582626</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.92008504782758</v>
+        <v>7.949513820271982</v>
       </c>
       <c r="D3" t="n">
-        <v>43.12530518859113</v>
+        <v>7.00786209314606</v>
       </c>
       <c r="E3" t="n">
-        <v>19.37026358447066</v>
+        <v>3.147667832476482</v>
       </c>
       <c r="F3" t="n">
-        <v>17.62451984973924</v>
+        <v>2.863984475582626</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>1.434409587320694</v>
+        <v>0.2330915579396127</v>
       </c>
       <c r="D4" t="n">
-        <v>3.605551275463989</v>
+        <v>0.5859020822628983</v>
       </c>
       <c r="E4" t="n">
-        <v>19.37026358447066</v>
+        <v>3.147667832476482</v>
       </c>
       <c r="F4" t="n">
-        <v>17.62451984973924</v>
+        <v>2.863984475582626</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.41636246629668</v>
+        <v>1.85515890077321</v>
       </c>
       <c r="D5" t="n">
-        <v>11.07372742687298</v>
+        <v>1.79948070686686</v>
       </c>
       <c r="E5" t="n">
-        <v>19.37026358447066</v>
+        <v>3.147667832476482</v>
       </c>
       <c r="F5" t="n">
-        <v>17.62451984973924</v>
+        <v>2.863984475582626</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
